--- a/資料庫/耆老訪談資料庫_1150608.xlsx
+++ b/資料庫/耆老訪談資料庫_1150608.xlsx
@@ -514,166 +514,166 @@
           <t>受訪同意書檔案名稱</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>錄音檔名</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>文字稿檔名</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>G001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>蘭潭（紅毛埤）</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>G001、G002</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>蘭潭（紅毛埤）、嘉義城隍廟</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>林阿水（虛構）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>E001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>1941-03</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>嘉義市東區○○路（虛構）</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>嘉義市東區</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>嘉義市東區</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>（範例資料，待替換）受訪者自幼在紅毛埤一帶長大，聽長輩說埤是「紅毛仔」（荷蘭人）所築，故稱紅毛埤。埤中央水最深處，地方人稱「紅毛埤底」，大人嚴禁小孩靠近。後來改稱蘭潭，老一輩仍習慣說紅毛埤。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>紅毛埤底、紅毛埤、埤仔頭</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>E001_01.jpg、E001_02.jpg、E001_03.jpg</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>E001_01.jpg、E001_02.jpg、E001_03.jpg、E001_04.jpg、E001_05.jpg、E001_06.jpg、E001_07.jpg、E001_08.jpg</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>E001_同意書.pdf</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>E001_訪談.m4a</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t>E001_文字稿.docx</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>G002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>嘉義城隍廟</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>王秀英（虛構）</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>E002</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>1938-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>嘉義市東區○○街（虛構）</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>嘉義市西區</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>嘉義市東區</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>（範例資料，待替換）受訪者婚後住在城隍廟附近，記得廟口早年有菜市與布攤，城外的頂菜園一帶多是菜園。長輩常說嘉義古早叫做諸羅山。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>諸羅山、頂菜園</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>E002_01.jpg、E002_02.jpg、E002_03.jpg</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>E002_同意書.pdf</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>E002_訪談.m4a</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>E002_文字稿.docx</t>
         </is>
